--- a/Caracterizacion_Haces/data/z12mm-822.xlsx
+++ b/Caracterizacion_Haces/data/z12mm-822.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="171">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,397 +128,415 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-874,3</t>
-  </si>
-  <si>
-    <t>96,37</t>
-  </si>
-  <si>
-    <t>85,33</t>
-  </si>
-  <si>
-    <t>99,58</t>
-  </si>
-  <si>
-    <t>81,57</t>
-  </si>
-  <si>
-    <t>85,14</t>
-  </si>
-  <si>
-    <t>83,64</t>
+    <t>707,9</t>
+  </si>
+  <si>
+    <t>93,37</t>
+  </si>
+  <si>
+    <t>89,13</t>
+  </si>
+  <si>
+    <t>100,6</t>
+  </si>
+  <si>
+    <t>80,90</t>
+  </si>
+  <si>
+    <t>88,62</t>
+  </si>
+  <si>
+    <t>84,10</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>-874,8</t>
-  </si>
-  <si>
-    <t>96,01</t>
-  </si>
-  <si>
-    <t>85,76</t>
-  </si>
-  <si>
-    <t>99,23</t>
-  </si>
-  <si>
-    <t>82,01</t>
-  </si>
-  <si>
-    <t>85,16</t>
-  </si>
-  <si>
-    <t>83,54</t>
+    <t>709,5</t>
+  </si>
+  <si>
+    <t>93,41</t>
+  </si>
+  <si>
+    <t>90,00</t>
+  </si>
+  <si>
+    <t>101,2</t>
+  </si>
+  <si>
+    <t>81,10</t>
+  </si>
+  <si>
+    <t>88,56</t>
+  </si>
+  <si>
+    <t>84,11</t>
   </si>
   <si>
     <t>0,4</t>
   </si>
   <si>
-    <t>-875,1</t>
-  </si>
-  <si>
-    <t>96,22</t>
-  </si>
-  <si>
-    <t>85,39</t>
-  </si>
-  <si>
-    <t>99,43</t>
-  </si>
-  <si>
-    <t>81,63</t>
-  </si>
-  <si>
-    <t>85,62</t>
-  </si>
-  <si>
-    <t>83,16</t>
+    <t>708,7</t>
+  </si>
+  <si>
+    <t>93,40</t>
+  </si>
+  <si>
+    <t>89,54</t>
+  </si>
+  <si>
+    <t>100,9</t>
+  </si>
+  <si>
+    <t>81,02</t>
+  </si>
+  <si>
+    <t>87,83</t>
+  </si>
+  <si>
+    <t>84,38</t>
   </si>
   <si>
     <t>0,6</t>
   </si>
   <si>
-    <t>-874,0</t>
-  </si>
-  <si>
-    <t>96,24</t>
-  </si>
-  <si>
-    <t>85,57</t>
-  </si>
-  <si>
-    <t>99,78</t>
-  </si>
-  <si>
-    <t>81,42</t>
-  </si>
-  <si>
-    <t>84,90</t>
-  </si>
-  <si>
-    <t>83,61</t>
+    <t>710,6</t>
+  </si>
+  <si>
+    <t>93,44</t>
+  </si>
+  <si>
+    <t>88,54</t>
+  </si>
+  <si>
+    <t>100,3</t>
+  </si>
+  <si>
+    <t>80,63</t>
+  </si>
+  <si>
+    <t>87,97</t>
+  </si>
+  <si>
+    <t>84,58</t>
   </si>
   <si>
     <t>0,8</t>
   </si>
   <si>
-    <t>-874,5</t>
-  </si>
-  <si>
-    <t>95,91</t>
-  </si>
-  <si>
-    <t>85,63</t>
-  </si>
-  <si>
-    <t>99,28</t>
-  </si>
-  <si>
-    <t>81,70</t>
-  </si>
-  <si>
-    <t>83,67</t>
+    <t>708,4</t>
+  </si>
+  <si>
+    <t>93,18</t>
+  </si>
+  <si>
+    <t>89,39</t>
+  </si>
+  <si>
+    <t>100,4</t>
+  </si>
+  <si>
+    <t>81,15</t>
+  </si>
+  <si>
+    <t>89,28</t>
+  </si>
+  <si>
+    <t>84,86</t>
   </si>
   <si>
     <t>1,0</t>
   </si>
   <si>
-    <t>-873,7</t>
-  </si>
-  <si>
-    <t>96,00</t>
-  </si>
-  <si>
-    <t>85,55</t>
-  </si>
-  <si>
-    <t>99,16</t>
-  </si>
-  <si>
-    <t>81,87</t>
-  </si>
-  <si>
-    <t>85,61</t>
+    <t>710,3</t>
+  </si>
+  <si>
+    <t>93,42</t>
+  </si>
+  <si>
+    <t>89,81</t>
+  </si>
+  <si>
+    <t>81,37</t>
+  </si>
+  <si>
+    <t>89,30</t>
+  </si>
+  <si>
+    <t>83,87</t>
   </si>
   <si>
     <t>1,2</t>
   </si>
   <si>
-    <t>96,07</t>
-  </si>
-  <si>
-    <t>85,72</t>
-  </si>
-  <si>
-    <t>99,57</t>
-  </si>
-  <si>
-    <t>81,62</t>
-  </si>
-  <si>
-    <t>85,49</t>
-  </si>
-  <si>
-    <t>83,55</t>
+    <t>93,15</t>
+  </si>
+  <si>
+    <t>87,01</t>
+  </si>
+  <si>
+    <t>98,73</t>
+  </si>
+  <si>
+    <t>80,62</t>
+  </si>
+  <si>
+    <t>88,43</t>
+  </si>
+  <si>
+    <t>84,42</t>
   </si>
   <si>
     <t>1,4</t>
   </si>
   <si>
-    <t>-875,3</t>
-  </si>
-  <si>
-    <t>96,39</t>
-  </si>
-  <si>
-    <t>99,91</t>
-  </si>
-  <si>
-    <t>81,41</t>
-  </si>
-  <si>
-    <t>85,45</t>
-  </si>
-  <si>
-    <t>83,59</t>
+    <t>709,0</t>
+  </si>
+  <si>
+    <t>93,38</t>
+  </si>
+  <si>
+    <t>89,07</t>
+  </si>
+  <si>
+    <t>100,5</t>
+  </si>
+  <si>
+    <t>80,96</t>
+  </si>
+  <si>
+    <t>87,92</t>
   </si>
   <si>
     <t>1,6</t>
   </si>
   <si>
-    <t>96,06</t>
-  </si>
-  <si>
-    <t>85,51</t>
+    <t>92,59</t>
+  </si>
+  <si>
+    <t>90,73</t>
+  </si>
+  <si>
+    <t>81,38</t>
+  </si>
+  <si>
+    <t>87,58</t>
+  </si>
+  <si>
+    <t>84,09</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>709,2</t>
+  </si>
+  <si>
+    <t>93,74</t>
+  </si>
+  <si>
+    <t>101,1</t>
+  </si>
+  <si>
+    <t>80,84</t>
+  </si>
+  <si>
+    <t>88,31</t>
+  </si>
+  <si>
+    <t>84,52</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>93,51</t>
+  </si>
+  <si>
+    <t>89,71</t>
+  </si>
+  <si>
+    <t>81,08</t>
+  </si>
+  <si>
+    <t>88,61</t>
+  </si>
+  <si>
+    <t>84,95</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>93,64</t>
+  </si>
+  <si>
+    <t>80,74</t>
+  </si>
+  <si>
+    <t>88,36</t>
+  </si>
+  <si>
+    <t>83,63</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>711,4</t>
+  </si>
+  <si>
+    <t>93,28</t>
+  </si>
+  <si>
+    <t>87,72</t>
   </si>
   <si>
     <t>99,29</t>
   </si>
   <si>
-    <t>81,73</t>
-  </si>
-  <si>
-    <t>85,11</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>-873,5</t>
-  </si>
-  <si>
-    <t>96,58</t>
-  </si>
-  <si>
-    <t>99,99</t>
-  </si>
-  <si>
-    <t>81,47</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>96,29</t>
-  </si>
-  <si>
-    <t>99,64</t>
-  </si>
-  <si>
-    <t>81,64</t>
-  </si>
-  <si>
-    <t>85,25</t>
-  </si>
-  <si>
-    <t>83,05</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>-875,6</t>
-  </si>
-  <si>
-    <t>96,33</t>
-  </si>
-  <si>
-    <t>85,58</t>
-  </si>
-  <si>
-    <t>81,96</t>
-  </si>
-  <si>
-    <t>85,21</t>
-  </si>
-  <si>
-    <t>83,58</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>95,75</t>
-  </si>
-  <si>
-    <t>98,96</t>
-  </si>
-  <si>
-    <t>81,81</t>
-  </si>
-  <si>
-    <t>85,01</t>
-  </si>
-  <si>
-    <t>83,72</t>
+    <t>80,86</t>
+  </si>
+  <si>
+    <t>87,80</t>
+  </si>
+  <si>
+    <t>84,69</t>
   </si>
   <si>
     <t>2,6</t>
   </si>
   <si>
-    <t>96,19</t>
-  </si>
-  <si>
-    <t>85,48</t>
-  </si>
-  <si>
-    <t>99,46</t>
-  </si>
-  <si>
-    <t>81,66</t>
-  </si>
-  <si>
-    <t>85,02</t>
-  </si>
-  <si>
-    <t>83,96</t>
+    <t>93,02</t>
+  </si>
+  <si>
+    <t>90,41</t>
+  </si>
+  <si>
+    <t>101,3</t>
+  </si>
+  <si>
+    <t>80,97</t>
+  </si>
+  <si>
+    <t>87,36</t>
+  </si>
+  <si>
+    <t>85,31</t>
   </si>
   <si>
     <t>2,8</t>
   </si>
   <si>
-    <t>96,32</t>
-  </si>
-  <si>
-    <t>99,61</t>
-  </si>
-  <si>
-    <t>85,15</t>
-  </si>
-  <si>
-    <t>83,99</t>
+    <t>93,83</t>
+  </si>
+  <si>
+    <t>87,26</t>
+  </si>
+  <si>
+    <t>99,55</t>
+  </si>
+  <si>
+    <t>80,67</t>
+  </si>
+  <si>
+    <t>88,65</t>
+  </si>
+  <si>
+    <t>84,85</t>
   </si>
   <si>
     <t>3,0</t>
   </si>
   <si>
-    <t>96,02</t>
-  </si>
-  <si>
-    <t>85,41</t>
-  </si>
-  <si>
-    <t>99,04</t>
-  </si>
-  <si>
-    <t>81,88</t>
-  </si>
-  <si>
-    <t>85,18</t>
-  </si>
-  <si>
-    <t>83,78</t>
+    <t>93,05</t>
+  </si>
+  <si>
+    <t>90,27</t>
+  </si>
+  <si>
+    <t>81,09</t>
+  </si>
+  <si>
+    <t>87,37</t>
+  </si>
+  <si>
+    <t>85,13</t>
   </si>
   <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>-873,2</t>
-  </si>
-  <si>
-    <t>96,59</t>
-  </si>
-  <si>
-    <t>85,64</t>
-  </si>
-  <si>
-    <t>100,2</t>
-  </si>
-  <si>
-    <t>81,35</t>
-  </si>
-  <si>
-    <t>85,32</t>
-  </si>
-  <si>
-    <t>84,16</t>
+    <t>93,08</t>
+  </si>
+  <si>
+    <t>89,11</t>
+  </si>
+  <si>
+    <t>80,89</t>
+  </si>
+  <si>
+    <t>88,41</t>
+  </si>
+  <si>
+    <t>84,27</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>96,36</t>
-  </si>
-  <si>
-    <t>85,79</t>
-  </si>
-  <si>
-    <t>82,04</t>
-  </si>
-  <si>
-    <t>85,23</t>
-  </si>
-  <si>
-    <t>83,93</t>
+    <t>93,07</t>
+  </si>
+  <si>
+    <t>89,18</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>81,16</t>
+  </si>
+  <si>
+    <t>88,72</t>
+  </si>
+  <si>
+    <t>83,90</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>85,31</t>
-  </si>
-  <si>
-    <t>99,24</t>
-  </si>
-  <si>
-    <t>81,75</t>
+    <t>89,61</t>
+  </si>
+  <si>
+    <t>100,7</t>
+  </si>
+  <si>
+    <t>80,91</t>
+  </si>
+  <si>
+    <t>87,34</t>
+  </si>
+  <si>
+    <t>84,19</t>
   </si>
   <si>
     <t>3,8</t>
   </si>
   <si>
-    <t>99,32</t>
-  </si>
-  <si>
-    <t>81,68</t>
-  </si>
-  <si>
-    <t>85,20</t>
-  </si>
-  <si>
-    <t>83,80</t>
+    <t>93,76</t>
+  </si>
+  <si>
+    <t>88,44</t>
+  </si>
+  <si>
+    <t>81,00</t>
+  </si>
+  <si>
+    <t>88,69</t>
+  </si>
+  <si>
+    <t>84,28</t>
   </si>
 </sst>
 </file>
@@ -859,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -867,7 +885,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59589120370370374</v>
+        <v>0.77341435185185192</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1008,7 +1026,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2657</v>
+        <v>1041</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1037,7 +1055,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2652</v>
+        <v>1041</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -1066,7 +1084,7 @@
         <v>50</v>
       </c>
       <c r="C25">
-        <v>2656</v>
+        <v>1040</v>
       </c>
       <c r="D25" t="s">
         <v>51</v>
@@ -1095,7 +1113,7 @@
         <v>58</v>
       </c>
       <c r="C26">
-        <v>2655</v>
+        <v>1042</v>
       </c>
       <c r="D26" t="s">
         <v>59</v>
@@ -1124,7 +1142,7 @@
         <v>66</v>
       </c>
       <c r="C27">
-        <v>2654</v>
+        <v>1041</v>
       </c>
       <c r="D27" t="s">
         <v>67</v>
@@ -1139,30 +1157,30 @@
         <v>70</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28">
-        <v>2654</v>
+        <v>1043</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
         <v>77</v>
@@ -1171,85 +1189,85 @@
         <v>78</v>
       </c>
       <c r="I28" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C29">
-        <v>2654</v>
+        <v>1042</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30">
+        <v>1043</v>
+      </c>
+      <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" t="s">
         <v>86</v>
-      </c>
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30">
-        <v>2652</v>
-      </c>
-      <c r="D30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" t="s">
-        <v>91</v>
-      </c>
-      <c r="I30" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C31">
-        <v>2653</v>
+        <v>1042</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="G31" t="s">
         <v>97</v>
@@ -1258,326 +1276,326 @@
         <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32">
-        <v>2655</v>
+        <v>1041</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="I32" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C33">
-        <v>2656</v>
+        <v>1042</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C34">
-        <v>2653</v>
+        <v>1044</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="C35">
-        <v>2653</v>
+        <v>1043</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G35" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C36">
-        <v>2654</v>
+        <v>1041</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>42</v>
       </c>
       <c r="C37">
-        <v>2655</v>
+        <v>1042</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="F37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G37" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="H37" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I37" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C38">
-        <v>2655</v>
+        <v>1042</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F38" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="C39">
-        <v>2657</v>
+        <v>1044</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F39" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I39" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
         <v>66</v>
       </c>
       <c r="C40">
-        <v>2655</v>
+        <v>1041</v>
       </c>
       <c r="D40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="G40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H40" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I40" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C41">
-        <v>2654</v>
+        <v>1041</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G41" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H41" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="I41" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C42">
-        <v>2655</v>
+        <v>1041</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="G42" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H42" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
